--- a/sheets/조재수대금교본/검수/대전 부루스.xlsx
+++ b/sheets/조재수대금교본/검수/대전 부루스.xlsx
@@ -2417,7 +2417,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -2447,11 +2447,7 @@
     </row>
     <row r="5" ht="117.77" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="23"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
@@ -2465,7 +2461,7 @@
         <is>
           <t xml:space="preserve">南
 –
-∧應南</t>
+應南</t>
         </is>
       </c>
       <c r="G5" s="23"/>
@@ -2517,8 +2513,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C7" s="22"/>
@@ -2691,7 +2686,7 @@
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-林ㄴ
+林
 –</t>
         </is>
       </c>
@@ -2727,8 +2722,7 @@
         <is>
           <t xml:space="preserve">–
 –
-應潢
-‹</t>
+應潢</t>
         </is>
       </c>
       <c r="C14" s="24"/>
@@ -2736,8 +2730,7 @@
         <is>
           <t xml:space="preserve">–
 –
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="E14" s="24"/>
@@ -2745,8 +2738,7 @@
         <is>
           <t xml:space="preserve">仲
 姑
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="G14" s="24"/>
@@ -2811,8 +2803,7 @@
       <c r="C17" s="23"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="E17" s="23"/>

--- a/sheets/조재수대금교본/검수/대전 부루스.xlsx
+++ b/sheets/조재수대금교본/검수/대전 부루스.xlsx
@@ -2417,7 +2417,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -2461,7 +2461,7 @@
         <is>
           <t xml:space="preserve">南
 –
-應南</t>
+∧應南</t>
         </is>
       </c>
       <c r="G5" s="23"/>
@@ -2686,7 +2686,7 @@
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-林
+林ㄴ
 –</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/대전 부루스.xlsx
+++ b/sheets/조재수대금교본/검수/대전 부루스.xlsx
@@ -2363,20 +2363,20 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="105.26" customHeight="true">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="117.77" customHeight="true">
+    <row r="3" ht="91.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="I3" s="22"/>
     </row>
-    <row r="4" ht="117.77" customHeight="true">
+    <row r="4" ht="91.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -2445,7 +2445,7 @@
       <c r="H4" s="21"/>
       <c r="I4" s="23"/>
     </row>
-    <row r="5" ht="117.77" customHeight="true">
+    <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I5" s="23"/>
     </row>
-    <row r="6" ht="117.77" customHeight="true">
+    <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="I6" s="24"/>
     </row>
-    <row r="7" ht="117.77" customHeight="true">
+    <row r="7" ht="91.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="I7" s="22"/>
     </row>
-    <row r="8" ht="117.77" customHeight="true">
+    <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I8" s="23"/>
     </row>
-    <row r="9" ht="117.77" customHeight="true">
+    <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
       <c r="H9" s="21"/>
       <c r="I9" s="23"/>
     </row>
-    <row r="10" ht="117.77" customHeight="true">
+    <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -2611,7 +2611,7 @@
       <c r="H10" s="21"/>
       <c r="I10" s="24"/>
     </row>
-    <row r="11" ht="117.77" customHeight="true">
+    <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="I11" s="22"/>
     </row>
-    <row r="12" ht="117.77" customHeight="true">
+    <row r="12" ht="91.25" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="I12" s="23"/>
     </row>
-    <row r="13" ht="117.77" customHeight="true">
+    <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" ht="117.77" customHeight="true">
+    <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="I14" s="24"/>
     </row>
-    <row r="15" ht="117.77" customHeight="true">
+    <row r="15" ht="91.25" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="I15" s="22"/>
     </row>
-    <row r="16" ht="117.77" customHeight="true">
+    <row r="16" ht="91.25" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -2797,7 +2797,7 @@
       <c r="H16" s="21"/>
       <c r="I16" s="23"/>
     </row>
-    <row r="17" ht="117.77" customHeight="true">
+    <row r="17" ht="91.25" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -2812,7 +2812,7 @@
       <c r="H17" s="21"/>
       <c r="I17" s="23"/>
     </row>
-    <row r="18" ht="117.77" customHeight="true">
+    <row r="18" ht="91.25" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -2841,6 +2841,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="38"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
 </worksheet>
 </file>